--- a/templates/taslak_ge.xlsx
+++ b/templates/taslak_ge.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakan.sahin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0959F7E-572B-4D89-99D2-A7F007CEDDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91677015-221B-4683-BD55-585C3812167F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="taslak_ge" sheetId="1" r:id="rId1"/>
+    <sheet name="ft." sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
